--- a/pds_admin_raj/Backend/Backend/Result_Sheet.xlsx
+++ b/pds_admin_raj/Backend/Backend/Result_Sheet.xlsx
@@ -1629,12 +1629,12 @@
     <t>PWS NEELKANTH WAEHOUSE HMH</t>
   </si>
   <si>
+    <t>PWS ABP AGRIWAREHOUSING HMO</t>
+  </si>
+  <si>
     <t>PWS PREETI ENTERPRISES HMO</t>
   </si>
   <si>
-    <t>PWS ABP AGRIWAREHOUSING HMO</t>
-  </si>
-  <si>
     <t xml:space="preserve">CWC BARAN </t>
   </si>
   <si>
@@ -1653,6 +1653,9 @@
     <t>PWS RAMDEV ENTERPRISES PILIBANGA</t>
   </si>
   <si>
+    <t>PWS RAJKUMARI PILIBANGA</t>
+  </si>
+  <si>
     <t>PWS AGGARWAL FOODS PILIBANGA</t>
   </si>
   <si>
@@ -1662,9 +1665,6 @@
     <t>PWS SUSHMA DEVI II PILIBANGA</t>
   </si>
   <si>
-    <t>PWS RAJKUMARI PILIBANGA</t>
-  </si>
-  <si>
     <t>PWS DARSHNA DEVI SANGARIA</t>
   </si>
   <si>
@@ -1854,15 +1854,15 @@
     <t>PWS REKHA DEVI JAITSAR</t>
   </si>
   <si>
+    <t>PWS RAJ WAREHOUSING JAITSAR</t>
+  </si>
+  <si>
+    <t>PWS MAMTA DEVI JAITSAR</t>
+  </si>
+  <si>
     <t>PWS MRG WAREHOUSE JAITSAR</t>
   </si>
   <si>
-    <t>PWS MAMTA DEVI JAITSAR</t>
-  </si>
-  <si>
-    <t>PWS RAJ WAREHOUSING JAITSAR</t>
-  </si>
-  <si>
     <t>PWS RELIABLE STATE SEEDS CORP KESRISINGHPUR</t>
   </si>
   <si>
@@ -1932,13 +1932,13 @@
     <t>PWS SUSHILA ARORA SURATGARH</t>
   </si>
   <si>
+    <t>PWS SHAKTI GRANARIES SURATGARH</t>
+  </si>
+  <si>
+    <t>PWS SANKHLA ENTERPRISES SURATGARH</t>
+  </si>
+  <si>
     <t>PWS SHAKTI GRAINRIES II SURATGARH</t>
-  </si>
-  <si>
-    <t>PWS SANKHLA ENTERPRISES SURATGARH</t>
-  </si>
-  <si>
-    <t>PWS SHAKTI GRANARIES SURATGARH</t>
   </si>
   <si>
     <t xml:space="preserve">RSWC BUNDI HATTIPURA UNIT II </t>
@@ -2974,7 +2974,7 @@
     <t>146_206</t>
   </si>
   <si>
-    <t>153_206</t>
+    <t>166_206</t>
   </si>
   <si>
     <t>139_207</t>
@@ -2983,12 +2983,12 @@
     <t>144_207</t>
   </si>
   <si>
+    <t>146_207</t>
+  </si>
+  <si>
     <t>153_207</t>
   </si>
   <si>
-    <t>166_207</t>
-  </si>
-  <si>
     <t>89_20</t>
   </si>
   <si>
@@ -3025,6 +3025,9 @@
     <t>149_232</t>
   </si>
   <si>
+    <t>150_232</t>
+  </si>
+  <si>
     <t>165_232</t>
   </si>
   <si>
@@ -3037,13 +3040,10 @@
     <t>138_233</t>
   </si>
   <si>
-    <t>147_233</t>
-  </si>
-  <si>
-    <t>150_233</t>
-  </si>
-  <si>
-    <t>135_234</t>
+    <t>165_233</t>
+  </si>
+  <si>
+    <t>165_234</t>
   </si>
   <si>
     <t>164_236</t>
@@ -3106,7 +3106,7 @@
     <t>154_250</t>
   </si>
   <si>
-    <t>154_251</t>
+    <t>141_251</t>
   </si>
   <si>
     <t>61_253</t>
@@ -3307,12 +3307,12 @@
     <t>102_327</t>
   </si>
   <si>
-    <t>101_329</t>
-  </si>
-  <si>
     <t>103_329</t>
   </si>
   <si>
+    <t>101_330</t>
+  </si>
+  <si>
     <t>103_330</t>
   </si>
   <si>
@@ -3511,18 +3511,18 @@
     <t>187_411</t>
   </si>
   <si>
-    <t>193_411</t>
+    <t>189_411</t>
   </si>
   <si>
     <t>195_411</t>
   </si>
   <si>
-    <t>189_412</t>
-  </si>
-  <si>
     <t>193_412</t>
   </si>
   <si>
+    <t>195_412</t>
+  </si>
+  <si>
     <t>186_415</t>
   </si>
   <si>
@@ -3643,7 +3643,7 @@
     <t>174_448</t>
   </si>
   <si>
-    <t>180_448</t>
+    <t>179_448</t>
   </si>
   <si>
     <t>182_448</t>
@@ -3994,7 +3994,7 @@
     <t>68_249</t>
   </si>
   <si>
-    <t>235_251</t>
+    <t>68_251</t>
   </si>
   <si>
     <t>73_251</t>
@@ -20780,7 +20780,7 @@
         <v>733</v>
       </c>
       <c r="S249">
-        <v>37740</v>
+        <v>22540</v>
       </c>
       <c r="T249" t="s">
         <v>984</v>
@@ -20824,7 +20824,7 @@
         <v>473</v>
       </c>
       <c r="L250">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="M250" t="s">
         <v>537</v>
@@ -20836,22 +20836,22 @@
         <v>32</v>
       </c>
       <c r="P250">
-        <v>29.54</v>
+        <v>29.56</v>
       </c>
       <c r="Q250">
-        <v>74.31999999999999</v>
+        <v>74.39</v>
       </c>
       <c r="R250" t="s">
         <v>733</v>
       </c>
       <c r="S250">
-        <v>45000</v>
+        <v>60200</v>
       </c>
       <c r="T250" t="s">
         <v>985</v>
       </c>
       <c r="U250">
-        <v>7.0924</v>
+        <v>7.3266</v>
       </c>
     </row>
     <row r="251" spans="1:21">
@@ -21019,10 +21019,10 @@
         <v>473</v>
       </c>
       <c r="L253">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="M253" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="N253" t="s">
         <v>22</v>
@@ -21031,22 +21031,22 @@
         <v>32</v>
       </c>
       <c r="P253">
-        <v>29.54</v>
+        <v>29.56</v>
       </c>
       <c r="Q253">
-        <v>74.31999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="R253" t="s">
         <v>733</v>
       </c>
       <c r="S253">
-        <v>22200</v>
+        <v>15200</v>
       </c>
       <c r="T253" t="s">
         <v>988</v>
       </c>
       <c r="U253">
-        <v>7.0924</v>
+        <v>7.7096</v>
       </c>
     </row>
     <row r="254" spans="1:21">
@@ -21084,7 +21084,7 @@
         <v>473</v>
       </c>
       <c r="L254">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="M254" t="s">
         <v>538</v>
@@ -21096,22 +21096,22 @@
         <v>32</v>
       </c>
       <c r="P254">
-        <v>29.56</v>
+        <v>29.54</v>
       </c>
       <c r="Q254">
-        <v>74.39</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="R254" t="s">
         <v>733</v>
       </c>
       <c r="S254">
-        <v>60200</v>
+        <v>67200</v>
       </c>
       <c r="T254" t="s">
         <v>989</v>
       </c>
       <c r="U254">
-        <v>7.3266</v>
+        <v>7.0924</v>
       </c>
     </row>
     <row r="255" spans="1:21">
@@ -21820,7 +21820,7 @@
         <v>733</v>
       </c>
       <c r="S265">
-        <v>15665.5</v>
+        <v>59878</v>
       </c>
       <c r="T265" t="s">
         <v>1000</v>
@@ -21929,7 +21929,7 @@
         <v>473</v>
       </c>
       <c r="L267">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="M267" t="s">
         <v>545</v>
@@ -21941,22 +21941,22 @@
         <v>32</v>
       </c>
       <c r="P267">
-        <v>29.47</v>
+        <v>29.51</v>
       </c>
       <c r="Q267">
-        <v>74.03</v>
+        <v>74.06</v>
       </c>
       <c r="R267" t="s">
         <v>733</v>
       </c>
       <c r="S267">
-        <v>89574.5</v>
+        <v>43400</v>
       </c>
       <c r="T267" t="s">
         <v>1002</v>
       </c>
       <c r="U267">
-        <v>6.3897</v>
+        <v>3.497</v>
       </c>
     </row>
     <row r="268" spans="1:21">
@@ -21979,10 +21979,10 @@
         <v>32</v>
       </c>
       <c r="G268">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H268" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I268">
         <v>29.49</v>
@@ -21994,7 +21994,7 @@
         <v>473</v>
       </c>
       <c r="L268">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M268" t="s">
         <v>546</v>
@@ -22006,22 +22006,22 @@
         <v>32</v>
       </c>
       <c r="P268">
-        <v>29.49</v>
+        <v>29.47</v>
       </c>
       <c r="Q268">
-        <v>74.06999999999999</v>
+        <v>74.03</v>
       </c>
       <c r="R268" t="s">
         <v>733</v>
       </c>
       <c r="S268">
-        <v>42647.5</v>
+        <v>1962</v>
       </c>
       <c r="T268" t="s">
         <v>1003</v>
       </c>
       <c r="U268">
-        <v>1.3595</v>
+        <v>6.3897</v>
       </c>
     </row>
     <row r="269" spans="1:21">
@@ -22059,7 +22059,7 @@
         <v>473</v>
       </c>
       <c r="L269">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M269" t="s">
         <v>547</v>
@@ -22124,10 +22124,10 @@
         <v>473</v>
       </c>
       <c r="L270">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M270" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="N270" t="s">
         <v>22</v>
@@ -22136,22 +22136,22 @@
         <v>32</v>
       </c>
       <c r="P270">
-        <v>29.46</v>
+        <v>29.49</v>
       </c>
       <c r="Q270">
-        <v>74.03</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="R270" t="s">
         <v>733</v>
       </c>
       <c r="S270">
-        <v>128070</v>
+        <v>44800</v>
       </c>
       <c r="T270" t="s">
         <v>1005</v>
       </c>
       <c r="U270">
-        <v>6.468</v>
+        <v>1.3595</v>
       </c>
     </row>
     <row r="271" spans="1:21">
@@ -22189,10 +22189,10 @@
         <v>473</v>
       </c>
       <c r="L271">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="M271" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="N271" t="s">
         <v>22</v>
@@ -22201,22 +22201,22 @@
         <v>32</v>
       </c>
       <c r="P271">
-        <v>29.55</v>
+        <v>29.46</v>
       </c>
       <c r="Q271">
-        <v>74.09</v>
+        <v>74.03</v>
       </c>
       <c r="R271" t="s">
         <v>733</v>
       </c>
       <c r="S271">
-        <v>44212.5</v>
+        <v>128070</v>
       </c>
       <c r="T271" t="s">
         <v>1006</v>
       </c>
       <c r="U271">
-        <v>8.161899999999999</v>
+        <v>6.468</v>
       </c>
     </row>
     <row r="272" spans="1:21">
@@ -22254,10 +22254,10 @@
         <v>473</v>
       </c>
       <c r="L272">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="M272" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N272" t="s">
         <v>22</v>
@@ -22266,22 +22266,22 @@
         <v>32</v>
       </c>
       <c r="P272">
-        <v>29.51</v>
+        <v>29.47</v>
       </c>
       <c r="Q272">
-        <v>74.06</v>
+        <v>74.03</v>
       </c>
       <c r="R272" t="s">
         <v>733</v>
       </c>
       <c r="S272">
-        <v>43400</v>
+        <v>85460</v>
       </c>
       <c r="T272" t="s">
         <v>1007</v>
       </c>
       <c r="U272">
-        <v>3.497</v>
+        <v>6.3897</v>
       </c>
     </row>
     <row r="273" spans="1:21">
@@ -22319,7 +22319,7 @@
         <v>473</v>
       </c>
       <c r="L273">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M273" t="s">
         <v>546</v>
@@ -22331,10 +22331,10 @@
         <v>32</v>
       </c>
       <c r="P273">
-        <v>29.49</v>
+        <v>29.47</v>
       </c>
       <c r="Q273">
-        <v>74.06999999999999</v>
+        <v>74.03</v>
       </c>
       <c r="R273" t="s">
         <v>733</v>
@@ -22346,7 +22346,7 @@
         <v>1008</v>
       </c>
       <c r="U273">
-        <v>1.3595</v>
+        <v>6.3897</v>
       </c>
     </row>
     <row r="274" spans="1:21">
@@ -23510,7 +23510,7 @@
         <v>733</v>
       </c>
       <c r="S291">
-        <v>48820</v>
+        <v>17710</v>
       </c>
       <c r="T291" t="s">
         <v>1026</v>
@@ -23640,7 +23640,7 @@
         <v>733</v>
       </c>
       <c r="S293">
-        <v>36090</v>
+        <v>67200</v>
       </c>
       <c r="T293" t="s">
         <v>1028</v>
@@ -23684,10 +23684,10 @@
         <v>473</v>
       </c>
       <c r="L294">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="M294" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="N294" t="s">
         <v>22</v>
@@ -23696,10 +23696,10 @@
         <v>32</v>
       </c>
       <c r="P294">
-        <v>29.56</v>
+        <v>29.51</v>
       </c>
       <c r="Q294">
-        <v>74.48999999999999</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="R294" t="s">
         <v>733</v>
@@ -23711,7 +23711,7 @@
         <v>1029</v>
       </c>
       <c r="U294">
-        <v>2.92</v>
+        <v>5.2222</v>
       </c>
     </row>
     <row r="295" spans="1:21">
@@ -28039,10 +28039,10 @@
         <v>473</v>
       </c>
       <c r="L361">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M361" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="N361" t="s">
         <v>22</v>
@@ -28051,22 +28051,22 @@
         <v>42</v>
       </c>
       <c r="P361">
-        <v>25.14431</v>
+        <v>25.06257</v>
       </c>
       <c r="Q361">
-        <v>75.8625</v>
+        <v>75.84820999999999</v>
       </c>
       <c r="R361" t="s">
         <v>733</v>
       </c>
       <c r="S361">
-        <v>17390.2</v>
+        <v>28520</v>
       </c>
       <c r="T361" t="s">
         <v>1096</v>
       </c>
       <c r="U361">
-        <v>14.5022</v>
+        <v>19.9043</v>
       </c>
     </row>
     <row r="362" spans="1:21">
@@ -28089,10 +28089,10 @@
         <v>42</v>
       </c>
       <c r="G362">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H362" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I362">
         <v>25.13</v>
@@ -28104,10 +28104,10 @@
         <v>473</v>
       </c>
       <c r="L362">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M362" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="N362" t="s">
         <v>22</v>
@@ -28116,22 +28116,22 @@
         <v>42</v>
       </c>
       <c r="P362">
-        <v>25.06257</v>
+        <v>25.14431</v>
       </c>
       <c r="Q362">
-        <v>75.84820999999999</v>
+        <v>75.8625</v>
       </c>
       <c r="R362" t="s">
         <v>733</v>
       </c>
       <c r="S362">
-        <v>11129.8</v>
+        <v>17390.2</v>
       </c>
       <c r="T362" t="s">
         <v>1097</v>
       </c>
       <c r="U362">
-        <v>19.9043</v>
+        <v>14.5022</v>
       </c>
     </row>
     <row r="363" spans="1:21">
@@ -28190,7 +28190,7 @@
         <v>733</v>
       </c>
       <c r="S363">
-        <v>27390</v>
+        <v>9999.799999999999</v>
       </c>
       <c r="T363" t="s">
         <v>1098</v>
@@ -32459,7 +32459,7 @@
         <v>473</v>
       </c>
       <c r="L429">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M429" t="s">
         <v>612</v>
@@ -32471,22 +32471,22 @@
         <v>47</v>
       </c>
       <c r="P429">
-        <v>29.37</v>
+        <v>29.35</v>
       </c>
       <c r="Q429">
-        <v>73.66</v>
+        <v>73.67</v>
       </c>
       <c r="R429" t="s">
         <v>733</v>
       </c>
       <c r="S429">
-        <v>37010</v>
+        <v>64400</v>
       </c>
       <c r="T429" t="s">
         <v>1164</v>
       </c>
       <c r="U429">
-        <v>1.3609</v>
+        <v>1.8846</v>
       </c>
     </row>
     <row r="430" spans="1:21">
@@ -32545,7 +32545,7 @@
         <v>733</v>
       </c>
       <c r="S430">
-        <v>64400</v>
+        <v>37010</v>
       </c>
       <c r="T430" t="s">
         <v>1165</v>
@@ -32589,7 +32589,7 @@
         <v>473</v>
       </c>
       <c r="L431">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M431" t="s">
         <v>614</v>
@@ -32601,22 +32601,22 @@
         <v>47</v>
       </c>
       <c r="P431">
-        <v>29.35</v>
+        <v>29.37</v>
       </c>
       <c r="Q431">
-        <v>73.67</v>
+        <v>73.66</v>
       </c>
       <c r="R431" t="s">
         <v>733</v>
       </c>
       <c r="S431">
-        <v>64400</v>
+        <v>44800</v>
       </c>
       <c r="T431" t="s">
         <v>1166</v>
       </c>
       <c r="U431">
-        <v>1.8846</v>
+        <v>1.3609</v>
       </c>
     </row>
     <row r="432" spans="1:21">
@@ -32654,10 +32654,10 @@
         <v>473</v>
       </c>
       <c r="L432">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M432" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N432" t="s">
         <v>22</v>
@@ -32666,22 +32666,22 @@
         <v>47</v>
       </c>
       <c r="P432">
-        <v>29.37</v>
+        <v>29.34</v>
       </c>
       <c r="Q432">
-        <v>73.66</v>
+        <v>73.67</v>
       </c>
       <c r="R432" t="s">
         <v>733</v>
       </c>
       <c r="S432">
-        <v>7790</v>
+        <v>27390</v>
       </c>
       <c r="T432" t="s">
         <v>1167</v>
       </c>
       <c r="U432">
-        <v>1.3609</v>
+        <v>3.4304</v>
       </c>
     </row>
     <row r="433" spans="1:21">
@@ -35319,7 +35319,7 @@
         <v>473</v>
       </c>
       <c r="L473">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M473" t="s">
         <v>638</v>
@@ -35452,7 +35452,7 @@
         <v>179</v>
       </c>
       <c r="M475" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="N475" t="s">
         <v>22</v>
@@ -35470,7 +35470,7 @@
         <v>733</v>
       </c>
       <c r="S475">
-        <v>33600</v>
+        <v>2920</v>
       </c>
       <c r="T475" t="s">
         <v>1210</v>
@@ -35517,7 +35517,7 @@
         <v>180</v>
       </c>
       <c r="M476" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N476" t="s">
         <v>22</v>
@@ -35535,7 +35535,7 @@
         <v>733</v>
       </c>
       <c r="S476">
-        <v>2920</v>
+        <v>33600</v>
       </c>
       <c r="T476" t="s">
         <v>1211</v>
@@ -42924,22 +42924,22 @@
         <v>473</v>
       </c>
       <c r="L590">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="M590" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="N590" t="s">
         <v>22</v>
       </c>
       <c r="O590" t="s">
-        <v>32</v>
+        <v>729</v>
       </c>
       <c r="P590">
-        <v>29.52</v>
+        <v>27.5</v>
       </c>
       <c r="Q590">
-        <v>74.51000000000001</v>
+        <v>75.61</v>
       </c>
       <c r="R590" t="s">
         <v>733</v>
@@ -42951,7 +42951,7 @@
         <v>1325</v>
       </c>
       <c r="U590">
-        <v>4.507</v>
+        <v>339.6464</v>
       </c>
     </row>
     <row r="591" spans="1:21">
@@ -43075,7 +43075,7 @@
         <v>733</v>
       </c>
       <c r="S592">
-        <v>14997</v>
+        <v>73400</v>
       </c>
       <c r="T592" t="s">
         <v>1327</v>
@@ -43270,7 +43270,7 @@
         <v>733</v>
       </c>
       <c r="S595">
-        <v>80470</v>
+        <v>22067</v>
       </c>
       <c r="T595" t="s">
         <v>1330</v>

--- a/pds_admin_raj/Backend/Backend/Result_Sheet.xlsx
+++ b/pds_admin_raj/Backend/Backend/Result_Sheet.xlsx
@@ -1629,12 +1629,12 @@
     <t>PWS NEELKANTH WAEHOUSE HMH</t>
   </si>
   <si>
+    <t>PWS PREETI ENTERPRISES HMO</t>
+  </si>
+  <si>
     <t>PWS ABP AGRIWAREHOUSING HMO</t>
   </si>
   <si>
-    <t>PWS PREETI ENTERPRISES HMO</t>
-  </si>
-  <si>
     <t xml:space="preserve">CWC BARAN </t>
   </si>
   <si>
@@ -1851,18 +1851,18 @@
     <t>PWS SUNIL SARAWAGI JAITSAR</t>
   </si>
   <si>
+    <t>PWS RAJ WAREHOUSING JAITSAR</t>
+  </si>
+  <si>
+    <t>PWS MRG WAREHOUSE JAITSAR</t>
+  </si>
+  <si>
+    <t>PWS MAMTA DEVI JAITSAR</t>
+  </si>
+  <si>
     <t>PWS REKHA DEVI JAITSAR</t>
   </si>
   <si>
-    <t>PWS RAJ WAREHOUSING JAITSAR</t>
-  </si>
-  <si>
-    <t>PWS MAMTA DEVI JAITSAR</t>
-  </si>
-  <si>
-    <t>PWS MRG WAREHOUSE JAITSAR</t>
-  </si>
-  <si>
     <t>PWS RELIABLE STATE SEEDS CORP KESRISINGHPUR</t>
   </si>
   <si>
@@ -1905,6 +1905,9 @@
     <t>PWS RAJ WAREHOUSING SBNR</t>
   </si>
   <si>
+    <t>PWS MALWA AGRO SBNR</t>
+  </si>
+  <si>
     <t>PWS MAJHA AGRO SBNR</t>
   </si>
   <si>
@@ -1923,22 +1926,19 @@
     <t>PWS ANITA GUPTA SRIKARANPUR</t>
   </si>
   <si>
-    <t>PWS MALWA AGRO SBNR</t>
-  </si>
-  <si>
     <t>PWS SUSHILA ENTERPRISES SURATGARH</t>
   </si>
   <si>
     <t>PWS SUSHILA ARORA SURATGARH</t>
   </si>
   <si>
+    <t>PWS SHAKTI GRAINRIES II SURATGARH</t>
+  </si>
+  <si>
+    <t>PWS SANKHLA ENTERPRISES SURATGARH</t>
+  </si>
+  <si>
     <t>PWS SHAKTI GRANARIES SURATGARH</t>
-  </si>
-  <si>
-    <t>PWS SANKHLA ENTERPRISES SURATGARH</t>
-  </si>
-  <si>
-    <t>PWS SHAKTI GRAINRIES II SURATGARH</t>
   </si>
   <si>
     <t xml:space="preserve">RSWC BUNDI HATTIPURA UNIT II </t>
@@ -2965,7 +2965,7 @@
     <t>155_203</t>
   </si>
   <si>
-    <t>161_203</t>
+    <t>160_203</t>
   </si>
   <si>
     <t>167_203</t>
@@ -2974,7 +2974,7 @@
     <t>146_206</t>
   </si>
   <si>
-    <t>166_206</t>
+    <t>153_206</t>
   </si>
   <si>
     <t>139_207</t>
@@ -2986,7 +2986,7 @@
     <t>146_207</t>
   </si>
   <si>
-    <t>153_207</t>
+    <t>166_207</t>
   </si>
   <si>
     <t>89_20</t>
@@ -3043,7 +3043,7 @@
     <t>165_233</t>
   </si>
   <si>
-    <t>165_234</t>
+    <t>136_234</t>
   </si>
   <si>
     <t>164_236</t>
@@ -3307,12 +3307,12 @@
     <t>102_327</t>
   </si>
   <si>
+    <t>101_329</t>
+  </si>
+  <si>
     <t>103_329</t>
   </si>
   <si>
-    <t>101_330</t>
-  </si>
-  <si>
     <t>103_330</t>
   </si>
   <si>
@@ -3508,21 +3508,21 @@
     <t>175_411</t>
   </si>
   <si>
-    <t>187_411</t>
-  </si>
-  <si>
     <t>189_411</t>
   </si>
   <si>
+    <t>193_411</t>
+  </si>
+  <si>
     <t>195_411</t>
   </si>
   <si>
+    <t>187_412</t>
+  </si>
+  <si>
     <t>193_412</t>
   </si>
   <si>
-    <t>195_412</t>
-  </si>
-  <si>
     <t>186_415</t>
   </si>
   <si>
@@ -3607,6 +3607,9 @@
     <t>188_440</t>
   </si>
   <si>
+    <t>196_440</t>
+  </si>
+  <si>
     <t>197_440</t>
   </si>
   <si>
@@ -3631,10 +3634,7 @@
     <t>205_443</t>
   </si>
   <si>
-    <t>196_444</t>
-  </si>
-  <si>
-    <t>197_444</t>
+    <t>188_444</t>
   </si>
   <si>
     <t>173_448</t>
@@ -3643,7 +3643,7 @@
     <t>174_448</t>
   </si>
   <si>
-    <t>179_448</t>
+    <t>180_448</t>
   </si>
   <si>
     <t>182_448</t>
@@ -20325,7 +20325,7 @@
         <v>733</v>
       </c>
       <c r="S242">
-        <v>71400</v>
+        <v>9060</v>
       </c>
       <c r="T242" t="s">
         <v>977</v>
@@ -20390,7 +20390,7 @@
         <v>733</v>
       </c>
       <c r="S243">
-        <v>117160</v>
+        <v>179500</v>
       </c>
       <c r="T243" t="s">
         <v>978</v>
@@ -20629,10 +20629,10 @@
         <v>473</v>
       </c>
       <c r="L247">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M247" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N247" t="s">
         <v>22</v>
@@ -20780,7 +20780,7 @@
         <v>733</v>
       </c>
       <c r="S249">
-        <v>22540</v>
+        <v>15540</v>
       </c>
       <c r="T249" t="s">
         <v>984</v>
@@ -20824,7 +20824,7 @@
         <v>473</v>
       </c>
       <c r="L250">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="M250" t="s">
         <v>537</v>
@@ -20836,22 +20836,22 @@
         <v>32</v>
       </c>
       <c r="P250">
-        <v>29.56</v>
+        <v>29.54</v>
       </c>
       <c r="Q250">
-        <v>74.39</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="R250" t="s">
         <v>733</v>
       </c>
       <c r="S250">
-        <v>60200</v>
+        <v>67200</v>
       </c>
       <c r="T250" t="s">
         <v>985</v>
       </c>
       <c r="U250">
-        <v>7.3266</v>
+        <v>7.0924</v>
       </c>
     </row>
     <row r="251" spans="1:21">
@@ -21040,7 +21040,7 @@
         <v>733</v>
       </c>
       <c r="S253">
-        <v>15200</v>
+        <v>22200</v>
       </c>
       <c r="T253" t="s">
         <v>988</v>
@@ -21084,7 +21084,7 @@
         <v>473</v>
       </c>
       <c r="L254">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="M254" t="s">
         <v>538</v>
@@ -21096,22 +21096,22 @@
         <v>32</v>
       </c>
       <c r="P254">
-        <v>29.54</v>
+        <v>29.56</v>
       </c>
       <c r="Q254">
-        <v>74.31999999999999</v>
+        <v>74.39</v>
       </c>
       <c r="R254" t="s">
         <v>733</v>
       </c>
       <c r="S254">
-        <v>67200</v>
+        <v>60200</v>
       </c>
       <c r="T254" t="s">
         <v>989</v>
       </c>
       <c r="U254">
-        <v>7.0924</v>
+        <v>7.3266</v>
       </c>
     </row>
     <row r="255" spans="1:21">
@@ -22145,7 +22145,7 @@
         <v>733</v>
       </c>
       <c r="S270">
-        <v>44800</v>
+        <v>42647.5</v>
       </c>
       <c r="T270" t="s">
         <v>1005</v>
@@ -22275,7 +22275,7 @@
         <v>733</v>
       </c>
       <c r="S272">
-        <v>85460</v>
+        <v>87612.5</v>
       </c>
       <c r="T272" t="s">
         <v>1007</v>
@@ -22319,10 +22319,10 @@
         <v>473</v>
       </c>
       <c r="L273">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="M273" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N273" t="s">
         <v>22</v>
@@ -22331,10 +22331,10 @@
         <v>32</v>
       </c>
       <c r="P273">
-        <v>29.47</v>
+        <v>29.49</v>
       </c>
       <c r="Q273">
-        <v>74.03</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="R273" t="s">
         <v>733</v>
@@ -22346,7 +22346,7 @@
         <v>1008</v>
       </c>
       <c r="U273">
-        <v>6.3897</v>
+        <v>1.3595</v>
       </c>
     </row>
     <row r="274" spans="1:21">
@@ -28039,10 +28039,10 @@
         <v>473</v>
       </c>
       <c r="L361">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M361" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="N361" t="s">
         <v>22</v>
@@ -28051,22 +28051,22 @@
         <v>42</v>
       </c>
       <c r="P361">
-        <v>25.06257</v>
+        <v>25.14431</v>
       </c>
       <c r="Q361">
-        <v>75.84820999999999</v>
+        <v>75.8625</v>
       </c>
       <c r="R361" t="s">
         <v>733</v>
       </c>
       <c r="S361">
-        <v>28520</v>
+        <v>17390.2</v>
       </c>
       <c r="T361" t="s">
         <v>1096</v>
       </c>
       <c r="U361">
-        <v>19.9043</v>
+        <v>14.5022</v>
       </c>
     </row>
     <row r="362" spans="1:21">
@@ -28089,10 +28089,10 @@
         <v>42</v>
       </c>
       <c r="G362">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H362" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I362">
         <v>25.13</v>
@@ -28104,10 +28104,10 @@
         <v>473</v>
       </c>
       <c r="L362">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M362" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="N362" t="s">
         <v>22</v>
@@ -28116,22 +28116,22 @@
         <v>42</v>
       </c>
       <c r="P362">
-        <v>25.14431</v>
+        <v>25.06257</v>
       </c>
       <c r="Q362">
-        <v>75.8625</v>
+        <v>75.84820999999999</v>
       </c>
       <c r="R362" t="s">
         <v>733</v>
       </c>
       <c r="S362">
-        <v>17390.2</v>
+        <v>11129.8</v>
       </c>
       <c r="T362" t="s">
         <v>1097</v>
       </c>
       <c r="U362">
-        <v>14.5022</v>
+        <v>19.9043</v>
       </c>
     </row>
     <row r="363" spans="1:21">
@@ -28190,7 +28190,7 @@
         <v>733</v>
       </c>
       <c r="S363">
-        <v>9999.799999999999</v>
+        <v>27390</v>
       </c>
       <c r="T363" t="s">
         <v>1098</v>
@@ -32394,7 +32394,7 @@
         <v>473</v>
       </c>
       <c r="L428">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M428" t="s">
         <v>611</v>
@@ -32406,7 +32406,7 @@
         <v>47</v>
       </c>
       <c r="P428">
-        <v>29.34</v>
+        <v>29.35</v>
       </c>
       <c r="Q428">
         <v>73.67</v>
@@ -32415,13 +32415,13 @@
         <v>733</v>
       </c>
       <c r="S428">
-        <v>36400</v>
+        <v>64400</v>
       </c>
       <c r="T428" t="s">
         <v>1163</v>
       </c>
       <c r="U428">
-        <v>3.4304</v>
+        <v>1.8846</v>
       </c>
     </row>
     <row r="429" spans="1:21">
@@ -32459,7 +32459,7 @@
         <v>473</v>
       </c>
       <c r="L429">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M429" t="s">
         <v>612</v>
@@ -32471,22 +32471,22 @@
         <v>47</v>
       </c>
       <c r="P429">
-        <v>29.35</v>
+        <v>29.37</v>
       </c>
       <c r="Q429">
-        <v>73.67</v>
+        <v>73.66</v>
       </c>
       <c r="R429" t="s">
         <v>733</v>
       </c>
       <c r="S429">
-        <v>64400</v>
+        <v>9010</v>
       </c>
       <c r="T429" t="s">
         <v>1164</v>
       </c>
       <c r="U429">
-        <v>1.8846</v>
+        <v>1.3609</v>
       </c>
     </row>
     <row r="430" spans="1:21">
@@ -32545,7 +32545,7 @@
         <v>733</v>
       </c>
       <c r="S430">
-        <v>37010</v>
+        <v>64400</v>
       </c>
       <c r="T430" t="s">
         <v>1165</v>
@@ -32589,7 +32589,7 @@
         <v>473</v>
       </c>
       <c r="L431">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M431" t="s">
         <v>614</v>
@@ -32601,22 +32601,22 @@
         <v>47</v>
       </c>
       <c r="P431">
-        <v>29.37</v>
+        <v>29.34</v>
       </c>
       <c r="Q431">
-        <v>73.66</v>
+        <v>73.67</v>
       </c>
       <c r="R431" t="s">
         <v>733</v>
       </c>
       <c r="S431">
-        <v>44800</v>
+        <v>36400</v>
       </c>
       <c r="T431" t="s">
         <v>1166</v>
       </c>
       <c r="U431">
-        <v>1.3609</v>
+        <v>3.4304</v>
       </c>
     </row>
     <row r="432" spans="1:21">
@@ -32654,10 +32654,10 @@
         <v>473</v>
       </c>
       <c r="L432">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M432" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N432" t="s">
         <v>22</v>
@@ -32666,22 +32666,22 @@
         <v>47</v>
       </c>
       <c r="P432">
-        <v>29.34</v>
+        <v>29.37</v>
       </c>
       <c r="Q432">
-        <v>73.67</v>
+        <v>73.66</v>
       </c>
       <c r="R432" t="s">
         <v>733</v>
       </c>
       <c r="S432">
-        <v>27390</v>
+        <v>35790</v>
       </c>
       <c r="T432" t="s">
         <v>1167</v>
       </c>
       <c r="U432">
-        <v>3.4304</v>
+        <v>1.3609</v>
       </c>
     </row>
     <row r="433" spans="1:21">
@@ -34495,7 +34495,7 @@
         <v>733</v>
       </c>
       <c r="S460">
-        <v>71700</v>
+        <v>5140</v>
       </c>
       <c r="T460" t="s">
         <v>1195</v>
@@ -34539,7 +34539,7 @@
         <v>473</v>
       </c>
       <c r="L461">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M461" t="s">
         <v>629</v>
@@ -34560,7 +34560,7 @@
         <v>733</v>
       </c>
       <c r="S461">
-        <v>56640</v>
+        <v>61600</v>
       </c>
       <c r="T461" t="s">
         <v>1196</v>
@@ -34589,22 +34589,22 @@
         <v>47</v>
       </c>
       <c r="G462">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H462" t="s">
-        <v>387</v>
+        <v>181</v>
       </c>
       <c r="I462">
-        <v>29.91</v>
+        <v>29.25</v>
       </c>
       <c r="J462">
-        <v>73.87</v>
+        <v>73.5</v>
       </c>
       <c r="K462" t="s">
         <v>473</v>
       </c>
       <c r="L462">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M462" t="s">
         <v>630</v>
@@ -34616,22 +34616,22 @@
         <v>47</v>
       </c>
       <c r="P462">
-        <v>29.85</v>
+        <v>29.31</v>
       </c>
       <c r="Q462">
-        <v>73.87</v>
+        <v>73.5</v>
       </c>
       <c r="R462" t="s">
         <v>733</v>
       </c>
       <c r="S462">
-        <v>74700</v>
+        <v>61600</v>
       </c>
       <c r="T462" t="s">
         <v>1197</v>
       </c>
       <c r="U462">
-        <v>7.1039</v>
+        <v>6.6553</v>
       </c>
     </row>
     <row r="463" spans="1:21">
@@ -34669,7 +34669,7 @@
         <v>473</v>
       </c>
       <c r="L463">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M463" t="s">
         <v>631</v>
@@ -34681,22 +34681,22 @@
         <v>47</v>
       </c>
       <c r="P463">
-        <v>29.93</v>
+        <v>29.85</v>
       </c>
       <c r="Q463">
-        <v>73.89</v>
+        <v>73.87</v>
       </c>
       <c r="R463" t="s">
         <v>733</v>
       </c>
       <c r="S463">
-        <v>144014.5</v>
+        <v>74700</v>
       </c>
       <c r="T463" t="s">
         <v>1198</v>
       </c>
       <c r="U463">
-        <v>6.6112</v>
+        <v>7.1039</v>
       </c>
     </row>
     <row r="464" spans="1:21">
@@ -34734,10 +34734,10 @@
         <v>473</v>
       </c>
       <c r="L464">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M464" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="N464" t="s">
         <v>22</v>
@@ -34746,22 +34746,22 @@
         <v>47</v>
       </c>
       <c r="P464">
-        <v>29.84</v>
+        <v>29.93</v>
       </c>
       <c r="Q464">
-        <v>73.88</v>
+        <v>73.89</v>
       </c>
       <c r="R464" t="s">
         <v>733</v>
       </c>
       <c r="S464">
-        <v>51285.5</v>
+        <v>144014.5</v>
       </c>
       <c r="T464" t="s">
         <v>1199</v>
       </c>
       <c r="U464">
-        <v>8.8574</v>
+        <v>6.6112</v>
       </c>
     </row>
     <row r="465" spans="1:21">
@@ -34784,10 +34784,10 @@
         <v>47</v>
       </c>
       <c r="G465">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H465" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I465">
         <v>29.91</v>
@@ -34799,10 +34799,10 @@
         <v>473</v>
       </c>
       <c r="L465">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="M465" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="N465" t="s">
         <v>22</v>
@@ -34811,22 +34811,22 @@
         <v>47</v>
       </c>
       <c r="P465">
-        <v>29.85</v>
+        <v>29.84</v>
       </c>
       <c r="Q465">
-        <v>73.87</v>
+        <v>73.88</v>
       </c>
       <c r="R465" t="s">
         <v>733</v>
       </c>
       <c r="S465">
-        <v>88500</v>
+        <v>51285.5</v>
       </c>
       <c r="T465" t="s">
         <v>1200</v>
       </c>
       <c r="U465">
-        <v>7.1039</v>
+        <v>8.8574</v>
       </c>
     </row>
     <row r="466" spans="1:21">
@@ -34864,10 +34864,10 @@
         <v>473</v>
       </c>
       <c r="L466">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="M466" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="N466" t="s">
         <v>22</v>
@@ -34876,22 +34876,22 @@
         <v>47</v>
       </c>
       <c r="P466">
-        <v>29.84</v>
+        <v>29.85</v>
       </c>
       <c r="Q466">
-        <v>73.88</v>
+        <v>73.87</v>
       </c>
       <c r="R466" t="s">
         <v>733</v>
       </c>
       <c r="S466">
-        <v>33684.5</v>
+        <v>88500</v>
       </c>
       <c r="T466" t="s">
         <v>1201</v>
       </c>
       <c r="U466">
-        <v>8.8574</v>
+        <v>7.1039</v>
       </c>
     </row>
     <row r="467" spans="1:21">
@@ -34914,25 +34914,25 @@
         <v>47</v>
       </c>
       <c r="G467">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H467" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I467">
-        <v>29.84</v>
+        <v>29.91</v>
       </c>
       <c r="J467">
-        <v>73.45999999999999</v>
+        <v>73.87</v>
       </c>
       <c r="K467" t="s">
         <v>473</v>
       </c>
       <c r="L467">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M467" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="N467" t="s">
         <v>22</v>
@@ -34944,19 +34944,19 @@
         <v>29.84</v>
       </c>
       <c r="Q467">
-        <v>73.48</v>
+        <v>73.88</v>
       </c>
       <c r="R467" t="s">
         <v>733</v>
       </c>
       <c r="S467">
-        <v>81500</v>
+        <v>33684.5</v>
       </c>
       <c r="T467" t="s">
         <v>1202</v>
       </c>
       <c r="U467">
-        <v>2.0395</v>
+        <v>8.8574</v>
       </c>
     </row>
     <row r="468" spans="1:21">
@@ -34994,7 +34994,7 @@
         <v>473</v>
       </c>
       <c r="L468">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M468" t="s">
         <v>634</v>
@@ -35009,19 +35009,19 @@
         <v>29.84</v>
       </c>
       <c r="Q468">
-        <v>73.48999999999999</v>
+        <v>73.48</v>
       </c>
       <c r="R468" t="s">
         <v>733</v>
       </c>
       <c r="S468">
-        <v>40300</v>
+        <v>81500</v>
       </c>
       <c r="T468" t="s">
         <v>1203</v>
       </c>
       <c r="U468">
-        <v>2.7765</v>
+        <v>2.0395</v>
       </c>
     </row>
     <row r="469" spans="1:21">
@@ -35044,22 +35044,22 @@
         <v>47</v>
       </c>
       <c r="G469">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H469" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I469">
-        <v>29.25</v>
+        <v>29.84</v>
       </c>
       <c r="J469">
-        <v>73.5</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="K469" t="s">
         <v>473</v>
       </c>
       <c r="L469">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="M469" t="s">
         <v>635</v>
@@ -35071,22 +35071,22 @@
         <v>47</v>
       </c>
       <c r="P469">
-        <v>29.31</v>
+        <v>29.84</v>
       </c>
       <c r="Q469">
-        <v>73.5</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="R469" t="s">
         <v>733</v>
       </c>
       <c r="S469">
-        <v>61600</v>
+        <v>40300</v>
       </c>
       <c r="T469" t="s">
         <v>1204</v>
       </c>
       <c r="U469">
-        <v>6.6553</v>
+        <v>2.7765</v>
       </c>
     </row>
     <row r="470" spans="1:21">
@@ -35124,10 +35124,10 @@
         <v>473</v>
       </c>
       <c r="L470">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="M470" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="N470" t="s">
         <v>22</v>
@@ -35136,7 +35136,7 @@
         <v>47</v>
       </c>
       <c r="P470">
-        <v>29.31</v>
+        <v>29.24</v>
       </c>
       <c r="Q470">
         <v>73.5</v>
@@ -35145,13 +35145,13 @@
         <v>733</v>
       </c>
       <c r="S470">
-        <v>4960</v>
+        <v>66560</v>
       </c>
       <c r="T470" t="s">
         <v>1205</v>
       </c>
       <c r="U470">
-        <v>6.6553</v>
+        <v>1.249</v>
       </c>
     </row>
     <row r="471" spans="1:21">
@@ -35319,7 +35319,7 @@
         <v>473</v>
       </c>
       <c r="L473">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M473" t="s">
         <v>638</v>
@@ -35452,7 +35452,7 @@
         <v>179</v>
       </c>
       <c r="M475" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N475" t="s">
         <v>22</v>
@@ -35470,7 +35470,7 @@
         <v>733</v>
       </c>
       <c r="S475">
-        <v>2920</v>
+        <v>33600</v>
       </c>
       <c r="T475" t="s">
         <v>1210</v>
@@ -35517,7 +35517,7 @@
         <v>180</v>
       </c>
       <c r="M476" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="N476" t="s">
         <v>22</v>
@@ -35535,7 +35535,7 @@
         <v>733</v>
       </c>
       <c r="S476">
-        <v>33600</v>
+        <v>2920</v>
       </c>
       <c r="T476" t="s">
         <v>1211</v>
